--- a/output/stock_quant_scores/TSMC34.SA_income_df.xlsx
+++ b/output/stock_quant_scores/TSMC34.SA_income_df.xlsx
@@ -1349,7 +1349,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>668450200000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1360,10 +1362,14 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>14.38125</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>592359200000</v>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
@@ -1392,9 +1398,13 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>819537300000</v>
+      </c>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>1587415000000</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
     </row>
   </sheetData>
